--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R90f2942f8c454327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R00333a34b7624112"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R8c3b6e075dd148d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R693f4478ba744e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R684839d06b914e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rfc930da1bc854a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R81284603a05540fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rfe2495bde2284479"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rea4817e9fd4341e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R08d3d7eea548449c"/>
   </x:sheets>
 </x:workbook>
 </file>
